--- a/Mantenimiento/excels/LIMA-LIMA-SAN_JUAN_DE_LURIGANCHO.xlsx
+++ b/Mantenimiento/excels/LIMA-LIMA-SAN_JUAN_DE_LURIGANCHO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L43"/>
+  <dimension ref="A1:K43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -484,11 +484,6 @@
           <t>siniestros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>mantenimiento</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -508,7 +503,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -536,11 +531,6 @@
       <c r="K2" t="n">
         <v>0</v>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -560,7 +550,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -588,11 +578,6 @@
       <c r="K3" t="n">
         <v>0</v>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -612,7 +597,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -640,11 +625,6 @@
       <c r="K4" t="n">
         <v>0</v>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -664,7 +644,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -692,11 +672,6 @@
       <c r="K5" t="n">
         <v>0</v>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -716,7 +691,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -744,11 +719,6 @@
       <c r="K6" t="n">
         <v>0</v>
       </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -768,7 +738,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -796,11 +766,6 @@
       <c r="K7" t="n">
         <v>0</v>
       </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -820,7 +785,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -848,11 +813,6 @@
       <c r="K8" t="n">
         <v>0</v>
       </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -872,7 +832,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -900,11 +860,6 @@
       <c r="K9" t="n">
         <v>0</v>
       </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -924,7 +879,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -952,11 +907,6 @@
       <c r="K10" t="n">
         <v>0</v>
       </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -976,7 +926,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1004,11 +954,6 @@
       <c r="K11" t="n">
         <v>0</v>
       </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1028,7 +973,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1056,11 +1001,6 @@
       <c r="K12" t="n">
         <v>0</v>
       </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1080,7 +1020,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1108,11 +1048,6 @@
       <c r="K13" t="n">
         <v>0</v>
       </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1132,7 +1067,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1160,11 +1095,6 @@
       <c r="K14" t="n">
         <v>0</v>
       </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1184,7 +1114,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1212,11 +1142,6 @@
       <c r="K15" t="n">
         <v>0</v>
       </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1236,7 +1161,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1264,11 +1189,6 @@
       <c r="K16" t="n">
         <v>0</v>
       </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1288,7 +1208,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1316,11 +1236,6 @@
       <c r="K17" t="n">
         <v>0</v>
       </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1340,7 +1255,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1368,11 +1283,6 @@
       <c r="K18" t="n">
         <v>0</v>
       </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1392,7 +1302,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1420,11 +1330,6 @@
       <c r="K19" t="n">
         <v>1</v>
       </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1444,7 +1349,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1472,11 +1377,6 @@
       <c r="K20" t="n">
         <v>0</v>
       </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1496,7 +1396,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1524,11 +1424,6 @@
       <c r="K21" t="n">
         <v>0</v>
       </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1548,7 +1443,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1576,11 +1471,6 @@
       <c r="K22" t="n">
         <v>0</v>
       </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1600,7 +1490,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1628,11 +1518,6 @@
       <c r="K23" t="n">
         <v>0</v>
       </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1652,7 +1537,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1680,11 +1565,6 @@
       <c r="K24" t="n">
         <v>0</v>
       </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1704,7 +1584,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1732,11 +1612,6 @@
       <c r="K25" t="n">
         <v>0</v>
       </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1756,7 +1631,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1784,11 +1659,6 @@
       <c r="K26" t="n">
         <v>0</v>
       </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1808,7 +1678,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1836,11 +1706,6 @@
       <c r="K27" t="n">
         <v>0</v>
       </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1860,7 +1725,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1888,11 +1753,6 @@
       <c r="K28" t="n">
         <v>0</v>
       </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1912,7 +1772,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1940,11 +1800,6 @@
       <c r="K29" t="n">
         <v>0</v>
       </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1964,7 +1819,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1992,11 +1847,6 @@
       <c r="K30" t="n">
         <v>0</v>
       </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2016,7 +1866,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2044,11 +1894,6 @@
       <c r="K31" t="n">
         <v>0</v>
       </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2068,7 +1913,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2096,11 +1941,6 @@
       <c r="K32" t="n">
         <v>0</v>
       </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2120,7 +1960,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2148,11 +1988,6 @@
       <c r="K33" t="n">
         <v>0</v>
       </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2172,7 +2007,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2200,11 +2035,6 @@
       <c r="K34" t="n">
         <v>0</v>
       </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2224,7 +2054,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2252,11 +2082,6 @@
       <c r="K35" t="n">
         <v>0</v>
       </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2276,7 +2101,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2304,11 +2129,6 @@
       <c r="K36" t="n">
         <v>0</v>
       </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2328,7 +2148,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2356,11 +2176,6 @@
       <c r="K37" t="n">
         <v>0</v>
       </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2380,7 +2195,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2408,11 +2223,6 @@
       <c r="K38" t="n">
         <v>0</v>
       </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2432,7 +2242,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2460,11 +2270,6 @@
       <c r="K39" t="n">
         <v>0</v>
       </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2484,7 +2289,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2512,11 +2317,6 @@
       <c r="K40" t="n">
         <v>0</v>
       </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2536,7 +2336,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2564,11 +2364,6 @@
       <c r="K41" t="n">
         <v>0</v>
       </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2588,7 +2383,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2616,11 +2411,6 @@
       <c r="K42" t="n">
         <v>0</v>
       </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2640,7 +2430,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2667,11 +2457,6 @@
       </c>
       <c r="K43" t="n">
         <v>0</v>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
       </c>
     </row>
   </sheetData>

--- a/Mantenimiento/excels/LIMA-LIMA-SAN_JUAN_DE_LURIGANCHO.xlsx
+++ b/Mantenimiento/excels/LIMA-LIMA-SAN_JUAN_DE_LURIGANCHO.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,57 +417,57 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>departamento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>distrito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>codigo_ce</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitud</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>alumnos</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>docentes</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>siniestros</t>
         </is>
@@ -516,20 +504,30 @@
           <t>0071 VIRGEN DEL CARMEN</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>-12.00289</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-77.01044</v>
-      </c>
-      <c r="I2" t="n">
-        <v>325</v>
-      </c>
-      <c r="J2" t="n">
-        <v>15</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-12.00289</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-77.01044</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>325</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -563,20 +561,30 @@
           <t>0084 VIRGEN MARIA</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>-11.99893</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-77.0021</v>
-      </c>
-      <c r="I3" t="n">
-        <v>452</v>
-      </c>
-      <c r="J3" t="n">
-        <v>19</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-11.99893</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-77.0021</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>452</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -610,20 +618,30 @@
           <t>0115 12 FLORES DE LIMA</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>-12.00937</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-77.00771</v>
-      </c>
-      <c r="I4" t="n">
-        <v>305</v>
-      </c>
-      <c r="J4" t="n">
-        <v>13</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-12.00937</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-77.00771</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>305</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -657,20 +675,30 @@
           <t>0045 SAN ANTONIO</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>-12.00468</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-77.01691</v>
-      </c>
-      <c r="I5" t="n">
-        <v>378</v>
-      </c>
-      <c r="J5" t="n">
-        <v>15</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-12.00468</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-77.01691</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>378</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -704,20 +732,30 @@
           <t>0086 JOSE MARIA ARGUEDAS</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>-11.97188</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-77.00235000000001</v>
-      </c>
-      <c r="I6" t="n">
-        <v>2029</v>
-      </c>
-      <c r="J6" t="n">
-        <v>79</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-11.97188</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-77.00235</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2029</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -751,20 +789,30 @@
           <t>0092 ALFRED NOBEL</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>-11.99857</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-77.00743</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1339</v>
-      </c>
-      <c r="J7" t="n">
-        <v>57</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-11.99857</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-77.00743</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1339</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -798,20 +846,30 @@
           <t>0132 TORIBIO DE LUZURIAGA Y MEJIA</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>-11.98134</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-77.01831</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1693</v>
-      </c>
-      <c r="J8" t="n">
-        <v>77</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-11.98134</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-77.01831</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1693</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -845,20 +903,30 @@
           <t>0134 MARIO FLORIAN</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>-12.01087</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-77.00667</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1113</v>
-      </c>
-      <c r="J9" t="n">
-        <v>46</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-12.01087</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-77.00667</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1113</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -892,20 +960,30 @@
           <t>0137 MIGUEL GRAU SEMINARIO</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>-11.98397</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-77.01347</v>
-      </c>
-      <c r="I10" t="n">
-        <v>1739</v>
-      </c>
-      <c r="J10" t="n">
-        <v>68</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-11.98397</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-77.01347</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1739</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -939,20 +1017,30 @@
           <t>0141 VIRGEN DE COCHARCAS</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>-11.96842</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-76.98842</v>
-      </c>
-      <c r="I11" t="n">
-        <v>907</v>
-      </c>
-      <c r="J11" t="n">
-        <v>35</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-11.96842</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-76.98842</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>907</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -986,20 +1074,30 @@
           <t>0147 CAPITAN EP LUIS ALBERTO GARCIA ROJAS</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>-11.99992</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-77.01264999999999</v>
-      </c>
-      <c r="I12" t="n">
-        <v>1384</v>
-      </c>
-      <c r="J12" t="n">
-        <v>52</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-11.99992</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-77.01265</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1384</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -1033,20 +1131,30 @@
           <t>0069 MACHU PICCHU</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>-11.97143</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-77.00932</v>
-      </c>
-      <c r="I13" t="n">
-        <v>885</v>
-      </c>
-      <c r="J13" t="n">
-        <v>39</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-11.97143</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-77.00932</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>885</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -1080,20 +1188,30 @@
           <t>0153 ALEJANDRO SANCHEZ ARTEAGA</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>-11.9622</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-76.99307</v>
-      </c>
-      <c r="I14" t="n">
-        <v>841</v>
-      </c>
-      <c r="J14" t="n">
-        <v>35</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-11.9622</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-76.99307</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>841</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -1127,20 +1245,30 @@
           <t>0168 AMISTAD PERU JAPON</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>-12.00328</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-77.00547</v>
-      </c>
-      <c r="I15" t="n">
-        <v>812</v>
-      </c>
-      <c r="J15" t="n">
-        <v>32</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-12.00328</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-77.00547</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>812</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -1174,20 +1302,30 @@
           <t>0169</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>-11.98876</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-77.00651999999999</v>
-      </c>
-      <c r="I16" t="n">
-        <v>1260</v>
-      </c>
-      <c r="J16" t="n">
-        <v>52</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-11.98876</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-77.00652</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1260</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -1221,20 +1359,30 @@
           <t>0171 01 JUAN VELASCO ALVARADO / 0171-01 JUAN VELASCO ALVARADO</t>
         </is>
       </c>
-      <c r="G17" t="n">
-        <v>-11.9351</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-76.98799</v>
-      </c>
-      <c r="I17" t="n">
-        <v>2134</v>
-      </c>
-      <c r="J17" t="n">
-        <v>87</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-11.9351</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-76.98799</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2134</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -1268,20 +1416,30 @@
           <t>0071 NUESTRA SEÑORA DE LA MERCED</t>
         </is>
       </c>
-      <c r="G18" t="n">
-        <v>-12.01674</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-77.01336999999999</v>
-      </c>
-      <c r="I18" t="n">
-        <v>880</v>
-      </c>
-      <c r="J18" t="n">
-        <v>49</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-12.01674</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-77.01337</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>880</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -1315,20 +1473,30 @@
           <t>0143 SOLIDARIDAD II</t>
         </is>
       </c>
-      <c r="G19" t="n">
-        <v>-12.01564</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-76.9648</v>
-      </c>
-      <c r="I19" t="n">
-        <v>500</v>
-      </c>
-      <c r="J19" t="n">
-        <v>28</v>
-      </c>
-      <c r="K19" t="n">
-        <v>1</v>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-12.01564</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-76.9648</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
     </row>
     <row r="20">
@@ -1362,20 +1530,30 @@
           <t>0140 SANTIAGO ANTUNEZ DE MAYOLO</t>
         </is>
       </c>
-      <c r="G20" t="n">
-        <v>-11.9766</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-77.00427000000001</v>
-      </c>
-      <c r="I20" t="n">
-        <v>1743</v>
-      </c>
-      <c r="J20" t="n">
-        <v>62</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-11.9766</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-77.00427</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1743</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="21">
@@ -1409,20 +1587,30 @@
           <t>0119 CANTO BELLO</t>
         </is>
       </c>
-      <c r="G21" t="n">
-        <v>-11.97731</v>
-      </c>
-      <c r="H21" t="n">
-        <v>-77.01824999999999</v>
-      </c>
-      <c r="I21" t="n">
-        <v>1017</v>
-      </c>
-      <c r="J21" t="n">
-        <v>43</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-11.97731</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-77.01825</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1017</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="22">
@@ -1456,20 +1644,30 @@
           <t>1172 CIRO ALEGRIA</t>
         </is>
       </c>
-      <c r="G22" t="n">
-        <v>-12.02335</v>
-      </c>
-      <c r="H22" t="n">
-        <v>-76.99959</v>
-      </c>
-      <c r="I22" t="n">
-        <v>856</v>
-      </c>
-      <c r="J22" t="n">
-        <v>38</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-12.02335</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-76.99959</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>856</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="23">
@@ -1503,20 +1701,30 @@
           <t>1173 JULIO CESAR TELLO</t>
         </is>
       </c>
-      <c r="G23" t="n">
-        <v>-12.01783</v>
-      </c>
-      <c r="H23" t="n">
-        <v>-77.00396000000001</v>
-      </c>
-      <c r="I23" t="n">
-        <v>914</v>
-      </c>
-      <c r="J23" t="n">
-        <v>38</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-12.01783</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-77.00396</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>914</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="24">
@@ -1550,20 +1758,30 @@
           <t>1181 ALBERT EINSTEIN</t>
         </is>
       </c>
-      <c r="G24" t="n">
-        <v>-12.00556</v>
-      </c>
-      <c r="H24" t="n">
-        <v>-77.01421000000001</v>
-      </c>
-      <c r="I24" t="n">
-        <v>988</v>
-      </c>
-      <c r="J24" t="n">
-        <v>48</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-12.00556</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>-77.01421</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>988</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="25">
@@ -1597,20 +1815,30 @@
           <t>RAMIRO PRIALE PRIALE</t>
         </is>
       </c>
-      <c r="G25" t="n">
-        <v>-11.96945</v>
-      </c>
-      <c r="H25" t="n">
-        <v>-76.98788999999999</v>
-      </c>
-      <c r="I25" t="n">
-        <v>992</v>
-      </c>
-      <c r="J25" t="n">
-        <v>46</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-11.96945</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>-76.98789</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>992</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="26">
@@ -1644,20 +1872,30 @@
           <t>SOLIDARIDAD III</t>
         </is>
       </c>
-      <c r="G26" t="n">
-        <v>-12.01247</v>
-      </c>
-      <c r="H26" t="n">
-        <v>-76.96263</v>
-      </c>
-      <c r="I26" t="n">
-        <v>399</v>
-      </c>
-      <c r="J26" t="n">
-        <v>26</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-12.01247</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>-76.96263</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>399</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="27">
@@ -1691,20 +1929,30 @@
           <t>0120 MANUEL ROBLES ALARCON</t>
         </is>
       </c>
-      <c r="G27" t="n">
-        <v>-11.95309</v>
-      </c>
-      <c r="H27" t="n">
-        <v>-76.99236999999999</v>
-      </c>
-      <c r="I27" t="n">
-        <v>1878</v>
-      </c>
-      <c r="J27" t="n">
-        <v>70</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-11.95309</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>-76.99237</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1878</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="28">
@@ -1738,20 +1986,30 @@
           <t>0113 DANIEL ALOMIA ROBLES</t>
         </is>
       </c>
-      <c r="G28" t="n">
-        <v>-12.00944</v>
-      </c>
-      <c r="H28" t="n">
-        <v>-77.00937</v>
-      </c>
-      <c r="I28" t="n">
-        <v>1889</v>
-      </c>
-      <c r="J28" t="n">
-        <v>73</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>-12.00944</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>-77.00937</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1889</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="29">
@@ -1785,20 +2043,30 @@
           <t>NUESTRA SEÑORA DEL ROSARIO</t>
         </is>
       </c>
-      <c r="G29" t="n">
-        <v>-11.97673</v>
-      </c>
-      <c r="H29" t="n">
-        <v>-76.99279</v>
-      </c>
-      <c r="I29" t="n">
-        <v>677</v>
-      </c>
-      <c r="J29" t="n">
-        <v>42</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>-11.97673</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>-76.99279</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>677</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="30">
@@ -1832,20 +2100,30 @@
           <t>FE Y ALEGRIA 32</t>
         </is>
       </c>
-      <c r="G30" t="n">
-        <v>-11.94083</v>
-      </c>
-      <c r="H30" t="n">
-        <v>-76.99132</v>
-      </c>
-      <c r="I30" t="n">
-        <v>1385</v>
-      </c>
-      <c r="J30" t="n">
-        <v>64</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>-11.94083</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>-76.99132</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1385</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="31">
@@ -1879,20 +2157,30 @@
           <t>MILAGROSA NUESTRA SEÑORA DEL CARMEN</t>
         </is>
       </c>
-      <c r="G31" t="n">
-        <v>-12.00813</v>
-      </c>
-      <c r="H31" t="n">
-        <v>-77.00659</v>
-      </c>
-      <c r="I31" t="n">
-        <v>578</v>
-      </c>
-      <c r="J31" t="n">
-        <v>14</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>-12.00813</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>-77.00659</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>578</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="32">
@@ -1926,20 +2214,30 @@
           <t>SAN JUAN DE LA SALLE</t>
         </is>
       </c>
-      <c r="G32" t="n">
-        <v>-11.99946</v>
-      </c>
-      <c r="H32" t="n">
-        <v>-77.00776</v>
-      </c>
-      <c r="I32" t="n">
-        <v>408</v>
-      </c>
-      <c r="J32" t="n">
-        <v>34</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0</v>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>-11.99946</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>-77.00776</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>408</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="33">
@@ -1973,20 +2271,30 @@
           <t>ANTON MAKARENKO</t>
         </is>
       </c>
-      <c r="G33" t="n">
-        <v>-11.98095</v>
-      </c>
-      <c r="H33" t="n">
-        <v>-76.99666000000001</v>
-      </c>
-      <c r="I33" t="n">
-        <v>315</v>
-      </c>
-      <c r="J33" t="n">
-        <v>22</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>-11.98095</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>-76.99666</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>315</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="34">
@@ -2020,20 +2328,30 @@
           <t>SHONA GARCIA VALLE</t>
         </is>
       </c>
-      <c r="G34" t="n">
-        <v>-12.02447</v>
-      </c>
-      <c r="H34" t="n">
-        <v>-77.00319</v>
-      </c>
-      <c r="I34" t="n">
-        <v>282</v>
-      </c>
-      <c r="J34" t="n">
-        <v>20</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>-12.02447</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>-77.00319</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="35">
@@ -2067,20 +2385,30 @@
           <t>DAVID AUSUBEL</t>
         </is>
       </c>
-      <c r="G35" t="n">
-        <v>-12.01139</v>
-      </c>
-      <c r="H35" t="n">
-        <v>-77.00981</v>
-      </c>
-      <c r="I35" t="n">
-        <v>478</v>
-      </c>
-      <c r="J35" t="n">
-        <v>30</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0</v>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>-12.01139</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>-77.00981</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>478</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="36">
@@ -2114,20 +2442,30 @@
           <t>DIEGO THOMSON</t>
         </is>
       </c>
-      <c r="G36" t="n">
-        <v>-12.00216</v>
-      </c>
-      <c r="H36" t="n">
-        <v>-76.99475</v>
-      </c>
-      <c r="I36" t="n">
-        <v>312</v>
-      </c>
-      <c r="J36" t="n">
-        <v>16</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0</v>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>-12.00216</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>-76.99475</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>312</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="37">
@@ -2161,20 +2499,30 @@
           <t>LA SORBONA DE LIMA</t>
         </is>
       </c>
-      <c r="G37" t="n">
-        <v>-12.02258</v>
-      </c>
-      <c r="H37" t="n">
-        <v>-76.97575000000001</v>
-      </c>
-      <c r="I37" t="n">
-        <v>404</v>
-      </c>
-      <c r="J37" t="n">
-        <v>21</v>
-      </c>
-      <c r="K37" t="n">
-        <v>0</v>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>-12.02258</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>-76.97575</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>404</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="38">
@@ -2208,20 +2556,30 @@
           <t>BERTOLT BRECHT BREZING</t>
         </is>
       </c>
-      <c r="G38" t="n">
-        <v>-11.98094</v>
-      </c>
-      <c r="H38" t="n">
-        <v>-77.00801</v>
-      </c>
-      <c r="I38" t="n">
-        <v>1017</v>
-      </c>
-      <c r="J38" t="n">
-        <v>56</v>
-      </c>
-      <c r="K38" t="n">
-        <v>0</v>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>-11.98094</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>-77.00801</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1017</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="39">
@@ -2255,20 +2613,30 @@
           <t>TRILCE WISSE</t>
         </is>
       </c>
-      <c r="G39" t="n">
-        <v>-11.97225</v>
-      </c>
-      <c r="H39" t="n">
-        <v>-76.99505000000001</v>
-      </c>
-      <c r="I39" t="n">
-        <v>625</v>
-      </c>
-      <c r="J39" t="n">
-        <v>22</v>
-      </c>
-      <c r="K39" t="n">
-        <v>0</v>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>-11.97225</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>-76.99505</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>625</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="40">
@@ -2302,20 +2670,30 @@
           <t>INNOVA SCHOOLS - SJL ARABISCOS</t>
         </is>
       </c>
-      <c r="G40" t="n">
-        <v>-12.01486</v>
-      </c>
-      <c r="H40" t="n">
-        <v>-77.00548000000001</v>
-      </c>
-      <c r="I40" t="n">
-        <v>1533</v>
-      </c>
-      <c r="J40" t="n">
-        <v>62</v>
-      </c>
-      <c r="K40" t="n">
-        <v>0</v>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>-12.01486</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>-77.00548</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1533</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="41">
@@ -2349,20 +2727,30 @@
           <t>INNOVA SCHOOLS - SJL EL SOL</t>
         </is>
       </c>
-      <c r="G41" t="n">
-        <v>-11.98165</v>
-      </c>
-      <c r="H41" t="n">
-        <v>-77.01018999999999</v>
-      </c>
-      <c r="I41" t="n">
-        <v>1240</v>
-      </c>
-      <c r="J41" t="n">
-        <v>51</v>
-      </c>
-      <c r="K41" t="n">
-        <v>0</v>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>-11.98165</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>-77.01019</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1240</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="42">
@@ -2396,20 +2784,30 @@
           <t>INGENIERIA DEL ESTE</t>
         </is>
       </c>
-      <c r="G42" t="n">
-        <v>-11.97208</v>
-      </c>
-      <c r="H42" t="n">
-        <v>-76.99316</v>
-      </c>
-      <c r="I42" t="n">
-        <v>588</v>
-      </c>
-      <c r="J42" t="n">
-        <v>17</v>
-      </c>
-      <c r="K42" t="n">
-        <v>0</v>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>-11.97208</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>-76.99316</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>588</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="43">
@@ -2443,20 +2841,30 @@
           <t>SANTO DOMINGO DE GUZMAN</t>
         </is>
       </c>
-      <c r="G43" t="n">
-        <v>-12.01877</v>
-      </c>
-      <c r="H43" t="n">
-        <v>-77.01044</v>
-      </c>
-      <c r="I43" t="n">
-        <v>1207</v>
-      </c>
-      <c r="J43" t="n">
-        <v>83</v>
-      </c>
-      <c r="K43" t="n">
-        <v>0</v>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>-12.01877</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>-77.01044</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1207</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
   </sheetData>
